--- a/개발 스케줄.xlsx
+++ b/개발 스케줄.xlsx
@@ -1,39 +1,120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29905"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795F2EB7-53E9-42B7-ADFC-7A1A911AA08F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9C127B3-7676-460C-859C-4BC0E41A9756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{5636ACCF-BBBA-4970-9AF5-FF8110B379E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>개발 스케줄</t>
+  </si>
+  <si>
+    <t>분류</t>
+  </si>
+  <si>
+    <t>항목</t>
+  </si>
+  <si>
+    <t>데이터 전처리</t>
+  </si>
+  <si>
+    <t>공공데이터 병합 및 정제</t>
+  </si>
+  <si>
+    <t>DB 스키마 설계 및 적재</t>
+  </si>
+  <si>
+    <t>머신러닝 모델링</t>
+  </si>
+  <si>
+    <t>교차상관함수 분석</t>
+  </si>
+  <si>
+    <t>시차 변수 및 이동평균 산출</t>
+  </si>
+  <si>
+    <t>스케일링 및 학습셋 결정</t>
+  </si>
+  <si>
+    <t>RF/XGB/LGBM 베이스라인 모델링</t>
+  </si>
+  <si>
+    <t>GridSearchCV 파라미터 튜닝</t>
+  </si>
+  <si>
+    <t>성능 지표 분석 및 최종 모델 확정</t>
+  </si>
+  <si>
+    <t>Back-End</t>
+  </si>
+  <si>
+    <t>Flask 기반 구조 설계 및 DB 연동</t>
+  </si>
+  <si>
+    <t>Raw Query 최적화 및 조회 API 개발</t>
+  </si>
+  <si>
+    <t>모델 서빙 및 실시간 추론 로직</t>
+  </si>
+  <si>
+    <t>데이터 자동 갱신 및 스케줄러 구현</t>
+  </si>
+  <si>
+    <t>Front-End</t>
+  </si>
+  <si>
+    <t>Bootstrap 5 레이아웃 및 대시보드 설계</t>
+  </si>
+  <si>
+    <t>Chart.js/지도 활용 시각화 기능 구현</t>
+  </si>
+  <si>
+    <t>마무리</t>
+  </si>
+  <si>
+    <t>최종 배포 및 결과 보고서 작성</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="m\/d\(aaa\)"/>
+    <numFmt numFmtId="176" formatCode="m\/d\(aaa\)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -49,16 +130,104 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5" tint="0.39997558519241921"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8" tint="0.39997558519241921"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFBC82FF"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF56A31C"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="30"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E9FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD9B3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4F1BE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBD9FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -66,17 +235,218 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -85,6 +455,20 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFD9B3"/>
+      <color rgb="FFFAFAFA"/>
+      <color rgb="FFF2F2F2"/>
+      <color rgb="FFBC82FF"/>
+      <color rgb="FF56A31C"/>
+      <color rgb="FF92F547"/>
+      <color rgb="FFD4F1BE"/>
+      <color rgb="FFEBD9FF"/>
+      <color rgb="FFE3EFFF"/>
+      <color rgb="FFD9E9FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -97,7 +481,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -393,88 +777,597 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5835DB04-4600-40EA-8FAA-AA7BD16F57DC}">
-  <dimension ref="C2:Z2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Z18"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="16.5" zeroHeight="1"/>
   <cols>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="34.375" style="1" customWidth="1"/>
+    <col min="3" max="26" width="7.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:26" x14ac:dyDescent="0.3">
-      <c r="C2" s="1">
+    <row r="1" spans="1:26" ht="69.75" customHeight="1">
+      <c r="A1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="18"/>
+      <c r="Z1" s="19"/>
+    </row>
+    <row r="2" spans="1:26" ht="35.25" customHeight="1">
+      <c r="A2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="26">
         <v>46098</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="26">
         <v>46099</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="26">
         <v>46100</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="26">
         <v>46101</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="26">
         <v>46104</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="26">
         <v>46105</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="26">
         <v>46106</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="26">
         <v>46107</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="26">
         <v>46108</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="26">
         <v>46111</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="26">
         <v>46112</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="26">
         <v>46113</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="26">
         <v>46114</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="26">
         <v>46115</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="26">
         <v>46118</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="26">
         <v>46119</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="26">
         <v>46120</v>
       </c>
-      <c r="T2" s="1">
+      <c r="T2" s="26">
         <v>46121</v>
       </c>
-      <c r="U2" s="1">
+      <c r="U2" s="26">
         <v>46122</v>
       </c>
-      <c r="V2" s="1">
+      <c r="V2" s="26">
         <v>46125</v>
       </c>
-      <c r="W2" s="1">
+      <c r="W2" s="26">
         <v>46126</v>
       </c>
-      <c r="X2" s="1">
+      <c r="X2" s="26">
         <v>46127</v>
       </c>
-      <c r="Y2" s="1">
+      <c r="Y2" s="26">
         <v>46128</v>
       </c>
-      <c r="Z2" s="1">
+      <c r="Z2" s="27">
         <v>46129</v>
       </c>
     </row>
+    <row r="3" spans="1:26" ht="35.25" customHeight="1">
+      <c r="A3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="9"/>
+    </row>
+    <row r="4" spans="1:26" ht="35.25" customHeight="1">
+      <c r="A4" s="8"/>
+      <c r="B4" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="9"/>
+    </row>
+    <row r="5" spans="1:26" ht="35.25" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="9"/>
+    </row>
+    <row r="6" spans="1:26" ht="35.25" customHeight="1">
+      <c r="A6" s="10"/>
+      <c r="B6" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="9"/>
+    </row>
+    <row r="7" spans="1:26" ht="35.25" customHeight="1">
+      <c r="A7" s="10"/>
+      <c r="B7" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="9"/>
+    </row>
+    <row r="8" spans="1:26" ht="35.25" customHeight="1">
+      <c r="A8" s="10"/>
+      <c r="B8" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="9"/>
+    </row>
+    <row r="9" spans="1:26" ht="35.25" customHeight="1">
+      <c r="A9" s="10"/>
+      <c r="B9" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="9"/>
+    </row>
+    <row r="10" spans="1:26" ht="35.25" customHeight="1">
+      <c r="A10" s="10"/>
+      <c r="B10" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="9"/>
+    </row>
+    <row r="11" spans="1:26" ht="35.25" customHeight="1">
+      <c r="A11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="9"/>
+    </row>
+    <row r="12" spans="1:26" ht="35.25" customHeight="1">
+      <c r="A12" s="11"/>
+      <c r="B12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="9"/>
+    </row>
+    <row r="13" spans="1:26" ht="35.25" customHeight="1">
+      <c r="A13" s="11"/>
+      <c r="B13" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="9"/>
+    </row>
+    <row r="14" spans="1:26" ht="35.25" customHeight="1">
+      <c r="A14" s="11"/>
+      <c r="B14" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+      <c r="X14" s="4"/>
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="9"/>
+    </row>
+    <row r="15" spans="1:26" ht="35.25" customHeight="1">
+      <c r="A15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="4"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="9"/>
+    </row>
+    <row r="16" spans="1:26" ht="35.25" customHeight="1">
+      <c r="A16" s="12"/>
+      <c r="B16" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="9"/>
+    </row>
+    <row r="17" spans="1:26" ht="35.25" customHeight="1">
+      <c r="A17" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="13"/>
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="13"/>
+      <c r="Z17" s="14"/>
+    </row>
+    <row r="18" spans="1:26" hidden="1">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+    </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:Z1"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A10"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/개발 스케줄.xlsx
+++ b/개발 스케줄.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9C127B3-7676-460C-859C-4BC0E41A9756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238A9CB3-6361-4C23-91F5-958A1161F80D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{5636ACCF-BBBA-4970-9AF5-FF8110B379E7}"/>
   </bookViews>
@@ -25,10 +25,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -114,7 +114,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m\/d\(aaa\)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,15 +170,15 @@
       <b/>
       <sz val="30"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1" tint="0.499984740745262"/>
+      <color rgb="FFEEB500"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -216,103 +216,23 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -326,39 +246,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -383,27 +277,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -413,40 +286,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -457,6 +330,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFEEB500"/>
       <color rgb="FFFFD9B3"/>
       <color rgb="FFFAFAFA"/>
       <color rgb="FFF2F2F2"/>
@@ -466,7 +340,6 @@
       <color rgb="FFD4F1BE"/>
       <color rgb="FFEBD9FF"/>
       <color rgb="FFE3EFFF"/>
-      <color rgb="FFD9E9FF"/>
     </mruColors>
   </colors>
   <extLst>
@@ -481,7 +354,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -778,128 +651,128 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5835DB04-4600-40EA-8FAA-AA7BD16F57DC}">
   <dimension ref="A1:Z18"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="16.5" zeroHeight="1"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="16.5" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="34.375" style="1" customWidth="1"/>
-    <col min="3" max="26" width="7.125" customWidth="1"/>
+    <col min="3" max="26" width="7.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="69.75" customHeight="1">
-      <c r="A1" s="20"/>
-      <c r="B1" s="21"/>
-      <c r="C1" s="18" t="s">
+    <row r="1" spans="1:26" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="19"/>
-    </row>
-    <row r="2" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A2" s="24" t="s">
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+    </row>
+    <row r="2" spans="1:26" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="14">
         <v>46098</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="14">
         <v>46099</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="14">
         <v>46100</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="14">
         <v>46101</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="14">
         <v>46104</v>
       </c>
-      <c r="H2" s="26">
+      <c r="H2" s="14">
         <v>46105</v>
       </c>
-      <c r="I2" s="26">
+      <c r="I2" s="14">
         <v>46106</v>
       </c>
-      <c r="J2" s="26">
+      <c r="J2" s="14">
         <v>46107</v>
       </c>
-      <c r="K2" s="26">
+      <c r="K2" s="14">
         <v>46108</v>
       </c>
-      <c r="L2" s="26">
+      <c r="L2" s="14">
         <v>46111</v>
       </c>
-      <c r="M2" s="26">
+      <c r="M2" s="14">
         <v>46112</v>
       </c>
-      <c r="N2" s="26">
+      <c r="N2" s="14">
         <v>46113</v>
       </c>
-      <c r="O2" s="26">
+      <c r="O2" s="14">
         <v>46114</v>
       </c>
-      <c r="P2" s="26">
+      <c r="P2" s="14">
         <v>46115</v>
       </c>
-      <c r="Q2" s="26">
+      <c r="Q2" s="14">
         <v>46118</v>
       </c>
-      <c r="R2" s="26">
+      <c r="R2" s="14">
         <v>46119</v>
       </c>
-      <c r="S2" s="26">
+      <c r="S2" s="14">
         <v>46120</v>
       </c>
-      <c r="T2" s="26">
+      <c r="T2" s="14">
         <v>46121</v>
       </c>
-      <c r="U2" s="26">
+      <c r="U2" s="14">
         <v>46122</v>
       </c>
-      <c r="V2" s="26">
+      <c r="V2" s="14">
         <v>46125</v>
       </c>
-      <c r="W2" s="26">
+      <c r="W2" s="14">
         <v>46126</v>
       </c>
-      <c r="X2" s="26">
+      <c r="X2" s="14">
         <v>46127</v>
       </c>
-      <c r="Y2" s="26">
+      <c r="Y2" s="14">
         <v>46128</v>
       </c>
-      <c r="Z2" s="27">
+      <c r="Z2" s="14">
         <v>46129</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:26" ht="35.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="3"/>
@@ -925,11 +798,11 @@
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
-      <c r="Z3" s="9"/>
-    </row>
-    <row r="4" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="22" t="s">
+      <c r="Z3" s="4"/>
+    </row>
+    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17"/>
+      <c r="B4" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="4"/>
@@ -955,13 +828,13 @@
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
-      <c r="Z4" s="9"/>
-    </row>
-    <row r="5" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="Z4" s="4"/>
+    </row>
+    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="4"/>
@@ -987,11 +860,11 @@
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
-      <c r="Z5" s="9"/>
-    </row>
-    <row r="6" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="15" t="s">
+      <c r="Z5" s="4"/>
+    </row>
+    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="4"/>
@@ -1017,11 +890,11 @@
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
-      <c r="Z6" s="9"/>
-    </row>
-    <row r="7" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A7" s="10"/>
-      <c r="B7" s="23" t="s">
+      <c r="Z6" s="4"/>
+    </row>
+    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="4"/>
@@ -1047,11 +920,11 @@
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
-      <c r="Z7" s="9"/>
-    </row>
-    <row r="8" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A8" s="10"/>
-      <c r="B8" s="15" t="s">
+      <c r="Z7" s="4"/>
+    </row>
+    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="18"/>
+      <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="4"/>
@@ -1077,11 +950,11 @@
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
-      <c r="Z8" s="9"/>
-    </row>
-    <row r="9" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A9" s="10"/>
-      <c r="B9" s="15" t="s">
+      <c r="Z8" s="4"/>
+    </row>
+    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="4"/>
@@ -1107,11 +980,11 @@
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
-      <c r="Z9" s="9"/>
-    </row>
-    <row r="10" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="15" t="s">
+      <c r="Z9" s="4"/>
+    </row>
+    <row r="10" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="4"/>
@@ -1137,13 +1010,13 @@
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
-      <c r="Z10" s="9"/>
-    </row>
-    <row r="11" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A11" s="11" t="s">
+      <c r="Z10" s="4"/>
+    </row>
+    <row r="11" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="4"/>
@@ -1169,11 +1042,11 @@
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
-      <c r="Z11" s="9"/>
-    </row>
-    <row r="12" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A12" s="11"/>
-      <c r="B12" s="16" t="s">
+      <c r="Z11" s="4"/>
+    </row>
+    <row r="12" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="19"/>
+      <c r="B12" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="4"/>
@@ -1199,11 +1072,11 @@
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
-      <c r="Z12" s="9"/>
-    </row>
-    <row r="13" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A13" s="11"/>
-      <c r="B13" s="16" t="s">
+      <c r="Z12" s="4"/>
+    </row>
+    <row r="13" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="19"/>
+      <c r="B13" s="9" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="4"/>
@@ -1229,11 +1102,11 @@
       <c r="W13" s="4"/>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
-      <c r="Z13" s="9"/>
-    </row>
-    <row r="14" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A14" s="11"/>
-      <c r="B14" s="16" t="s">
+      <c r="Z13" s="4"/>
+    </row>
+    <row r="14" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="19"/>
+      <c r="B14" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="4"/>
@@ -1259,13 +1132,13 @@
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
-      <c r="Z14" s="9"/>
-    </row>
-    <row r="15" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A15" s="12" t="s">
+      <c r="Z14" s="4"/>
+    </row>
+    <row r="15" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
       <c r="C15" s="4"/>
@@ -1291,11 +1164,11 @@
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
-      <c r="Z15" s="9"/>
-    </row>
-    <row r="16" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A16" s="12"/>
-      <c r="B16" s="17" t="s">
+      <c r="Z15" s="4"/>
+    </row>
+    <row r="16" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="20"/>
+      <c r="B16" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="4"/>
@@ -1321,41 +1194,41 @@
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
       <c r="Y16" s="7"/>
-      <c r="Z16" s="9"/>
-    </row>
-    <row r="17" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A17" s="29" t="s">
+      <c r="Z16" s="4"/>
+    </row>
+    <row r="17" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="13"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="13"/>
-      <c r="Z17" s="14"/>
-    </row>
-    <row r="18" spans="1:26" hidden="1">
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="21"/>
+    </row>
+    <row r="18" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
     </row>
